--- a/demandes_en_attente.xlsx
+++ b/demandes_en_attente.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>Last Name</t>
   </si>
@@ -47,6 +47,21 @@
   </si>
   <si>
     <t>entreprise</t>
+  </si>
+  <si>
+    <t>erick_eapa@outlook.com</t>
+  </si>
+  <si>
+    <t>Eduardo</t>
+  </si>
+  <si>
+    <t>Polanco</t>
+  </si>
+  <si>
+    <t>8293527272</t>
+  </si>
+  <si>
+    <t>Example</t>
   </si>
 </sst>
 </file>
@@ -404,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -442,6 +457,26 @@
         <v>10</v>
       </c>
     </row>
+    <row r="2" spans="1:11">
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/demandes_en_attente.xlsx
+++ b/demandes_en_attente.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Last Name</t>
   </si>
@@ -47,21 +47,6 @@
   </si>
   <si>
     <t>entreprise</t>
-  </si>
-  <si>
-    <t>erick_eapa@outlook.com</t>
-  </si>
-  <si>
-    <t>Eduardo</t>
-  </si>
-  <si>
-    <t>Polanco</t>
-  </si>
-  <si>
-    <t>8293527272</t>
-  </si>
-  <si>
-    <t>Example</t>
   </si>
 </sst>
 </file>
@@ -419,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -457,26 +442,6 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/demandes_en_attente.xlsx
+++ b/demandes_en_attente.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Last Name</t>
   </si>
@@ -47,6 +47,9 @@
   </si>
   <si>
     <t>entreprise</t>
+  </si>
+  <si>
+    <t>Entreprise</t>
   </si>
 </sst>
 </file>
@@ -404,10 +407,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -440,6 +443,9 @@
       </c>
       <c r="K1" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/demandes_en_attente.xlsx
+++ b/demandes_en_attente.xlsx
@@ -1,81 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>Last Name</t>
-  </si>
-  <si>
-    <t>First Name</t>
-  </si>
-  <si>
-    <t>Phone</t>
-  </si>
-  <si>
-    <t>Role</t>
-  </si>
-  <si>
-    <t>Company</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Nom</t>
-  </si>
-  <si>
-    <t>Prenom</t>
-  </si>
-  <si>
-    <t>Téléphone</t>
-  </si>
-  <si>
-    <t>Rôle</t>
-  </si>
-  <si>
-    <t>entreprise</t>
-  </si>
-  <si>
-    <t>Entreprise</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -90,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -406,49 +420,117 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Last Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>First Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Prenom</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Téléphone</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Rôle</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>entreprise</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Entreprise</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Prénom</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>evaqu185@gmail.com</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>eva</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>etudiante</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>epf</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>qu</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/demandes_en_attente.xlsx
+++ b/demandes_en_attente.xlsx
@@ -1,37 +1,99 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Nom</t>
+  </si>
+  <si>
+    <t>Prenom</t>
+  </si>
+  <si>
+    <t>Téléphone</t>
+  </si>
+  <si>
+    <t>Rôle</t>
+  </si>
+  <si>
+    <t>entreprise</t>
+  </si>
+  <si>
+    <t>Entreprise</t>
+  </si>
+  <si>
+    <t>Prénom</t>
+  </si>
+  <si>
+    <t>evaqu185@gmail.com</t>
+  </si>
+  <si>
+    <t>eva</t>
+  </si>
+  <si>
+    <t>etudiante</t>
+  </si>
+  <si>
+    <t>epf</t>
+  </si>
+  <si>
+    <t>qu</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +108,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,117 +424,69 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Last Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Nom</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Prenom</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Téléphone</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Rôle</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>entreprise</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Entreprise</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Prénom</t>
-        </is>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>evaqu185@gmail.com</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>eva</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>etudiante</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>epf</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>qu</t>
-        </is>
+    <row r="2" spans="1:13">
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/demandes_en_attente.xlsx
+++ b/demandes_en_attente.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Last Name</t>
   </si>
@@ -53,21 +53,6 @@
   </si>
   <si>
     <t>Prénom</t>
-  </si>
-  <si>
-    <t>evaqu185@gmail.com</t>
-  </si>
-  <si>
-    <t>eva</t>
-  </si>
-  <si>
-    <t>etudiante</t>
-  </si>
-  <si>
-    <t>epf</t>
-  </si>
-  <si>
-    <t>qu</t>
   </si>
 </sst>
 </file>
@@ -425,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -469,23 +454,6 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" t="s">
-        <v>17</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/demandes_en_attente.xlsx
+++ b/demandes_en_attente.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="22">
   <si>
     <t>Last Name</t>
   </si>
@@ -53,6 +53,33 @@
   </si>
   <si>
     <t>Prénom</t>
+  </si>
+  <si>
+    <t>erick.gargolas@outlook.com</t>
+  </si>
+  <si>
+    <t>erick.gagolas@outlook.com</t>
+  </si>
+  <si>
+    <t>erick.gagolas@olook.com</t>
+  </si>
+  <si>
+    <t>erk.gagolas@olook.com</t>
+  </si>
+  <si>
+    <t>erk.gagolas@olook.c</t>
+  </si>
+  <si>
+    <t>Arrindell</t>
+  </si>
+  <si>
+    <t>Accumed</t>
+  </si>
+  <si>
+    <t>sdas</t>
+  </si>
+  <si>
+    <t>Eduardo</t>
   </si>
 </sst>
 </file>
@@ -410,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -454,6 +481,106 @@
         <v>12</v>
       </c>
     </row>
+    <row r="2" spans="1:13">
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2">
+        <v>744943369</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3">
+        <v>744943369</v>
+      </c>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4">
+        <v>744943369</v>
+      </c>
+      <c r="J4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5">
+        <v>744943369</v>
+      </c>
+      <c r="J5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6">
+        <v>744943369</v>
+      </c>
+      <c r="J6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M6" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/demandes_en_attente.xlsx
+++ b/demandes_en_attente.xlsx
@@ -1,37 +1,63 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+  <si>
+    <t>Nom</t>
+  </si>
+  <si>
+    <t>Prénom</t>
+  </si>
+  <si>
+    <t>Téléphone</t>
+  </si>
+  <si>
+    <t>Rôle</t>
+  </si>
+  <si>
+    <t>Entreprise</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +72,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,229 +388,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Nom</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Prénom</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Téléphone</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Rôle</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Entreprise</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>antonio</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Arrindell</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>33</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Student</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>accumed</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>erick.gargolas@gmail.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>jose</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>baez</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>744943369</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Student</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>accumed</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ed.polanco.arr@gmail.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>maria</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>perez</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>34466575655</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Student</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>accumed</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>jose.baez@gmail.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Teresa</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Arrabales</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>49642134</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Student</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>accumed</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Teresa.arrabales@hotmail.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Faira</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Peralos</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>84420043632</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Student</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>accumed</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>F.peralos@gmail.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Gojo</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Satoru</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0744943369</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Exorcist</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Soul Asociation</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>G.Satoru@gmail.com</t>
-        </is>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/demandes_en_attente.xlsx
+++ b/demandes_en_attente.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Nom</t>
   </si>
@@ -32,6 +32,21 @@
   </si>
   <si>
     <t>Email</t>
+  </si>
+  <si>
+    <t>Arrindell</t>
+  </si>
+  <si>
+    <t>Eduardo</t>
+  </si>
+  <si>
+    <t>sdfsd</t>
+  </si>
+  <si>
+    <t>dfgd</t>
+  </si>
+  <si>
+    <t>erick@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -389,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -412,6 +427,26 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>744943369</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/demandes_en_attente.xlsx
+++ b/demandes_en_attente.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Nom</t>
   </si>
@@ -32,21 +32,6 @@
   </si>
   <si>
     <t>Email</t>
-  </si>
-  <si>
-    <t>Arrindell</t>
-  </si>
-  <si>
-    <t>Eduardo</t>
-  </si>
-  <si>
-    <t>sdfsd</t>
-  </si>
-  <si>
-    <t>dfgd</t>
-  </si>
-  <si>
-    <t>erick@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -404,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -427,26 +412,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>744943369</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
